--- a/data/trans_bre/P1429-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1429-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,47</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>443,68%</t>
+          <t>437,22%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,06</t>
+          <t>0,57; 4,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,94</t>
+          <t>1,31; 4,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,57</t>
+          <t>2,11; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,31</t>
+          <t>3,12; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,45; 499,61</t>
+          <t>5,19; 482,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,46; —</t>
+          <t>91,51; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>269,8; —</t>
+          <t>259,87; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>175,52; 972,04</t>
+          <t>173,64; 1002,31</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>534,95%</t>
+          <t>417,17%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,01</t>
+          <t>1,01; 4,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,15</t>
+          <t>2,53; 4,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,39</t>
+          <t>1,99; 4,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,64</t>
+          <t>2,51; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,68; 456,16</t>
+          <t>46,28; 512,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>222,55; 3943,63</t>
+          <t>245,64; 3614,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>214,02; 1484,43</t>
+          <t>188,49; 1022,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>456,63%</t>
+          <t>646,26%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,4</t>
+          <t>3,64; 7,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,71</t>
+          <t>1,87; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,35</t>
+          <t>2,23; 5,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,28</t>
+          <t>2,69; 5,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>352,3; 5354,39</t>
+          <t>366,67; 5616,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>181,24; —</t>
+          <t>228,65; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,12; 1413,39</t>
+          <t>212,53; 1997,96</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>4,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>351,07%</t>
+          <t>439,94%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,8</t>
+          <t>2,04; 4,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,22</t>
+          <t>4,13; 7,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,53</t>
+          <t>1,33; 3,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,74</t>
+          <t>2,68; 5,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>123,31; 832,45</t>
+          <t>128,67; 831,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>697,41; —</t>
+          <t>644,26; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>131,19; 2413,69</t>
+          <t>147,18; 2846,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,14; 1014,62</t>
+          <t>82,46; 1192,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,58</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>436,41%</t>
+          <t>467,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,06</t>
+          <t>2,51; 4,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,6</t>
+          <t>3,16; 4,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,85</t>
+          <t>2,44; 3,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,31</t>
+          <t>3,29; 4,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>191,88; 533,47</t>
+          <t>190,19; 498,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>707,08; 6020,21</t>
+          <t>780,69; 5624,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>442,93; 1859,53</t>
+          <t>477,85; 1886,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>230,18; 733,67</t>
+          <t>261,49; 724,91</t>
         </is>
       </c>
     </row>
